--- a/ps2/ps2_output/table_1.xlsx
+++ b/ps2/ps2_output/table_1.xlsx
@@ -397,7 +397,7 @@
         <v>5.9597170171992513</v>
       </c>
       <c r="C2" s="2">
-        <v>4.2589738815219071</v>
+        <v>4.2589738815219072</v>
       </c>
       <c r="D2">
         <v>1.7007431356773441</v>
